--- a/education_surveys/034_light_pollution_awareness_survey--education_surveys.xlsx
+++ b/education_surveys/034_light_pollution_awareness_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_100,_'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 100, 'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_200,_'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 200, 'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_300,_'label':_'neither'}</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 300, 'label': 'Neither'}</t>
+          <t>Neither</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_400,_'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 400, 'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_500,_'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 500, 'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_100,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 100, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_200,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 200, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_300,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 300, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_400,_'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 400, 'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_100,_'label':_'less'}</t>
+          <t>less</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 100, 'label': 'Less'}</t>
+          <t>Less</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_200,_'label':_'more'}</t>
+          <t>more</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 200, 'label': 'More'}</t>
+          <t>More</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_300,_'label':_'much_more'}</t>
+          <t>much_more</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 300, 'label': 'Much More'}</t>
+          <t>Much More</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_400,_'label':_'much_much_more'}</t>
+          <t>much_much_more</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 400, 'label': 'Much Much More'}</t>
+          <t>Much Much More</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_100,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 100, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_200,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 200, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_300,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 300, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_400,_'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 400, 'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
